--- a/engine/chart2/qa/extras/data/xlsx/regionMap.xlsx
+++ b/engine/chart2/qa/extras/data/xlsx/regionMap.xlsx
@@ -163,6 +163,7 @@
         <cx:series layoutId="regionMap" uniqueId="{CDBD2114-7EDA-4606-BAEB-B992A137855E}">
           <cx:dataId val="0"/>
           <cx:layoutPr>
+            <cx:regionLabelLayout val="bestFitOnly"/>
             <cx:geography cultureLanguage="en-US" cultureRegion="GB" attribution="Powered by Bing">
               <cx:geoCache provider="{E9337A44-BEBE-4D9F-B70C-5C5E7DAFC167}">
                 <cx:binary>7HvJkt24kuWvpOWmN81IEgMBlFU+swJ5b8yDxghpQ4sRAMERIAmC39V/0D/WHpoyFaXKfM8qzbIX
